--- a/Export_Vorlage/Schächte.xlsx
+++ b/Export_Vorlage/Schächte.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Schaechte" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schaechte" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schaechte'!$A$26:$Q$5000</definedName>
@@ -770,13 +770,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -796,10 +796,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -816,10 +816,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF6600"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -836,10 +836,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -856,10 +856,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="AEB135"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -876,10 +876,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="92D050"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -895,8 +895,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -945,10 +945,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -957,13 +957,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -983,10 +983,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="92D050"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1003,10 +1003,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="E7E6E6"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1023,10 +1023,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1042,8 +1042,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1092,10 +1092,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1104,13 +1104,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1130,10 +1130,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="548235"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1150,10 +1150,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1170,10 +1170,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF8000"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1190,10 +1190,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00B0F0"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1210,10 +1210,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1229,8 +1229,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1279,10 +1279,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1291,13 +1291,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1317,10 +1317,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="548235"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1337,10 +1337,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="BF8F00"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1357,10 +1357,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00B0F0"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1377,10 +1377,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="7030A0"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1397,10 +1397,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="D6DCE4"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1416,8 +1416,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1466,10 +1466,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1478,13 +1478,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1504,10 +1504,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1524,10 +1524,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00B050"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1544,10 +1544,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="D6DCE4"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1563,8 +1563,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1613,10 +1613,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1625,13 +1625,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1651,17 +1651,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4472C4"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1669,10 +1669,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8497B0"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1680,10 +1680,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="D6DCE4"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1702,8 +1702,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="0"/>
               </a:pPr>
@@ -1734,8 +1734,8 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="700" b="0"/>
             </a:pPr>
@@ -1764,10 +1764,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1776,13 +1776,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1802,17 +1802,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9DC3E6"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1820,10 +1820,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="76A5AF"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1831,10 +1831,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4472C4"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1842,10 +1842,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="2F5597"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1853,10 +1853,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8497B0"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1864,10 +1864,10 @@
           <dPt>
             <idx val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="44546A"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1886,8 +1886,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="0"/>
               </a:pPr>
@@ -1918,8 +1918,8 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="700" b="0"/>
             </a:pPr>
@@ -1948,10 +1948,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1960,7 +1960,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
     <pos x="3024000" y="72000"/>
     <ext cx="4680000" cy="558000"/>
@@ -1970,9 +1970,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1987,9 +1987,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2004,9 +2004,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2021,9 +2021,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2038,9 +2038,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2055,9 +2055,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId6"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2072,9 +2072,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId7"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2089,13 +2089,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2565,11 +2565,11 @@
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
-          <t>AWU</t>
+          <t>Abwasser Uri</t>
         </is>
       </c>
       <c r="K17" s="12">
-        <f>COUNTIF($J$27:$J$5000,"AWU")</f>
+        <f>COUNTIF($J$27:$J$5000,"Abwasser Uri")+COUNTIF($J$27:$J$5000,"AWU")</f>
         <v/>
       </c>
       <c r="L17" s="15" t="inlineStr">
@@ -2633,11 +2633,11 @@
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>Kanton</t>
+          <t>Kanton Uri</t>
         </is>
       </c>
       <c r="K18" s="12">
-        <f>COUNTIF($J$27:$J$5000,"Kanton")</f>
+        <f>COUNTIF($J$27:$J$5000,"Kanton Uri")+COUNTIF($J$27:$J$5000,"Kanton")</f>
         <v/>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -3148,31 +3148,37 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:J5000">
     <cfRule type="expression" priority="16" dxfId="0" stopIfTrue="1">
+      <formula>$J27="Abwasser Uri"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" dxfId="0" stopIfTrue="1">
       <formula>$J27="AWU"</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" dxfId="6" stopIfTrue="1">
+    <cfRule type="expression" priority="18" dxfId="6" stopIfTrue="1">
+      <formula>$J27="Kanton Uri"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="19" dxfId="6" stopIfTrue="1">
       <formula>$J27="Kanton"</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" dxfId="10" stopIfTrue="1">
+    <cfRule type="expression" priority="20" dxfId="10" stopIfTrue="1">
       <formula>$J27="Bund"</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
       <formula>$J27="Gemeinde"</formula>
     </cfRule>
-    <cfRule type="expression" priority="20" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="22" dxfId="4" stopIfTrue="1">
       <formula>$J27="Privat"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:P5000">
-    <cfRule type="expression" priority="21" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="23" dxfId="4" stopIfTrue="1">
       <formula>$P27="offen"</formula>
     </cfRule>
-    <cfRule type="expression" priority="22" dxfId="11" stopIfTrue="1">
+    <cfRule type="expression" priority="24" dxfId="11" stopIfTrue="1">
       <formula>$P27="abgeschlossen"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:Q5000">
-    <cfRule type="expression" priority="23" dxfId="12">
+    <cfRule type="expression" priority="25" dxfId="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
